--- a/docs/Iteration #3 Feature Log .xlsx
+++ b/docs/Iteration #3 Feature Log .xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marve\Desktop\RenCloud\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{688B4D27-A0A0-4AE1-A012-208B7E9FE0F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{398E20D9-673F-4CE8-ABC9-CB15DBBCFBB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3760" yWindow="1580" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,9 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
   <si>
-    <t>Iteration #1</t>
-  </si>
-  <si>
     <t>Feature</t>
   </si>
   <si>
@@ -114,6 +111,9 @@
   </si>
   <si>
     <t>Providing user with the uploaded video length based on the ruller, having thumbinals to showcase different parts of a video. Also Thumbinal processing handled with use of ffmpeg.</t>
+  </si>
+  <si>
+    <t>Iteration #3</t>
   </si>
 </sst>
 </file>
@@ -197,7 +197,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -525,93 +525,93 @@
   <sheetData>
     <row r="1" spans="1:8" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -620,22 +620,22 @@
     </row>
     <row r="6" spans="1:8" ht="64" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
